--- a/Result/UKG_Result_Template.xlsx
+++ b/Result/UKG_Result_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\garuw\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\garuw\OneDrive\Documents\GitHub\jagdamba\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102E42A1-AEFF-4982-A086-ABD342C1A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCE1247-704B-4868-B692-FF8A43499C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,8 +580,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.625" bestFit="1" customWidth="1"/>
@@ -592,7 +592,7 @@
     <col min="7" max="17" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -645,7 +645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -698,7 +698,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -742,7 +742,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -795,7 +795,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -848,7 +848,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -901,7 +901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -954,7 +954,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1466,7 +1466,6 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
